--- a/batchstudent/Result/anlpvhe187047/TC2/GradeDetail.xlsx
+++ b/batchstudent/Result/anlpvhe187047/TC2/GradeDetail.xlsx
@@ -158,10 +158,10 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN_SENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASS</x:t>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -170,28 +170,10 @@
     <x:t>Server responding (SYN-ACK)</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Connection established</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RESET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -218,7 +200,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -227,17 +209,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -260,7 +232,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -270,14 +242,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -287,14 +253,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -921,11 +879,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R7"/>
+  <x:dimension ref="A1:R4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1032,25 +990,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0">
-        <x:v>54906</x:v>
-      </x:c>
-      <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>47</x:v>
@@ -1088,7 +1046,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1108,8 +1066,8 @@
       <x:c r="Q3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R3" s="3" t="s">
-        <x:v>51</x:v>
+      <x:c r="R3" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1129,10 +1087,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1144,7 +1102,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>17</x:v>
@@ -1164,176 +1122,8 @@
       <x:c r="Q4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R4" s="3" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:18">
-      <x:c r="A5" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P5" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q5" s="0">
-        <x:v>54906</x:v>
-      </x:c>
-      <x:c r="R5" s="4" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:18">
-      <x:c r="A6" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P6" s="0">
-        <x:v>44836</x:v>
-      </x:c>
-      <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R6" s="4" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:18">
-      <x:c r="A7" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q7" s="0">
-        <x:v>44836</x:v>
-      </x:c>
-      <x:c r="R7" s="4" t="s">
-        <x:v>57</x:v>
+      <x:c r="R4" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
